--- a/03_ai-threat-modeling-mitre-atlas/demo/threat_model_demo.xlsx
+++ b/03_ai-threat-modeling-mitre-atlas/demo/threat_model_demo.xlsx
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>ATLAS structures External Harms (AML.T0048) into sub-techniques. The financial-loss case is captured precisely by AML.T0048.001 "Financial Harm" — ATLAS uses the term "Financial Harm" in the catalog.</t>
+          <t>ATLAS structures External Harms (AML.T0048) into sub-techniques. The financial-loss case is captured precisely by AML.T0048.000 "Financial Harm" — ATLAS uses the term "Financial Harm" in the catalog.</t>
         </is>
       </c>
     </row>

--- a/03_ai-threat-modeling-mitre-atlas/demo/threat_model_demo.xlsx
+++ b/03_ai-threat-modeling-mitre-atlas/demo/threat_model_demo.xlsx
@@ -911,12 +911,12 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>ML Model Inference API Access</t>
+          <t>AI Model Inference API Access</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>ML Model Access</t>
+          <t>AI Model Access</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
@@ -1061,6 +1061,7 @@
       <c r="D2" s="16" t="n"/>
       <c r="E2" s="17" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -1156,7 +1157,7 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>ML Model Inference API Access</t>
+          <t>AI Model Inference API Access</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
@@ -1168,6 +1169,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
@@ -1227,7 +1229,7 @@
     <row r="14" ht="96" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>AML.T0040 — ML Model Inference API Access</t>
+          <t>AML.T0040 — AI Model Inference API Access</t>
         </is>
       </c>
       <c r="B14" s="17" t="n"/>
@@ -1239,6 +1241,7 @@
       <c r="D14" s="16" t="n"/>
       <c r="E14" s="17" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
@@ -1278,6 +1281,7 @@
       <c r="D18" s="16" t="n"/>
       <c r="E18" s="17" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
@@ -1417,6 +1421,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
@@ -1485,6 +1490,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
@@ -1640,7 +1646,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Evade ML Model</t>
+          <t>Evade AI Model</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -1662,7 +1668,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Backdoor ML Model</t>
+          <t>Backdoor AI Model</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -1706,7 +1712,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Exfiltration via ML Inference API</t>
+          <t>Exfiltration via AI Inference API</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -1728,7 +1734,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Denial of ML Service</t>
+          <t>Denial of AI Service</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -1750,12 +1756,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>ML Model Inference API Access</t>
+          <t>AI Model Inference API Access</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>ML Model Access</t>
+          <t>AI Model Access</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -1794,12 +1800,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Full ML Model Access</t>
+          <t>Full AI Model Access</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>ML Model Access</t>
+          <t>AI Model Access</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -2050,7 +2056,7 @@
       </c>
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>ATLAS lists Backdoor ML Model under both "Persistence" and "ML Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
+          <t>ATLAS lists Backdoor AI Model under both "Persistence" and "ML Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
         </is>
       </c>
     </row>

--- a/03_ai-threat-modeling-mitre-atlas/demo/threat_model_demo.xlsx
+++ b/03_ai-threat-modeling-mitre-atlas/demo/threat_model_demo.xlsx
@@ -1783,7 +1783,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>ML Attack Staging</t>
+          <t>AI Attack Staging</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>ATLAS lists Backdoor AI Model under both "Persistence" and "ML Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
+          <t>ATLAS lists Backdoor AI Model under both "Persistence" and "AI Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
         </is>
       </c>
     </row>
